--- a/public/exports/64942212.xlsx
+++ b/public/exports/64942212.xlsx
@@ -8394,7 +8394,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009464</t>
+          <t xml:space="preserve">200009460</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559430</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559430</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559430</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -27714,7 +27714,7 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559430</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -27774,7 +27774,7 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559430</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">

--- a/public/exports/64942212.xlsx
+++ b/public/exports/64942212.xlsx
@@ -8394,7 +8394,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009460</t>
+          <t xml:space="preserve">200009454</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031555</t>
+          <t xml:space="preserve">311031569</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031555</t>
+          <t xml:space="preserve">311031569</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031555</t>
+          <t xml:space="preserve">311031569</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t xml:space="preserve">311509832</t>
+          <t xml:space="preserve">311509833</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -26874,7 +26874,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559469</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559469</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559468</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559464</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559464</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -27234,7 +27234,7 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559473</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559466</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559465</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559470</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559472</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559461</t>
+          <t xml:space="preserve">311559432</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568903</t>
+          <t xml:space="preserve">311568904</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
@@ -35214,7 +35214,7 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590480</t>
+          <t xml:space="preserve">311590478</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
@@ -36594,7 +36594,7 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606933</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
@@ -36654,7 +36654,7 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606933</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
@@ -36714,7 +36714,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606933</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606933</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
@@ -36834,7 +36834,7 @@
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606933</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J614" t="inlineStr">
@@ -36894,7 +36894,7 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606933</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
@@ -37014,7 +37014,7 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606929</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
@@ -37074,7 +37074,7 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606929</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
@@ -37194,7 +37194,7 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606931</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
@@ -37254,7 +37254,7 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606925</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
@@ -37494,7 +37494,7 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606932</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
@@ -37554,7 +37554,7 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606932</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
@@ -37614,7 +37614,7 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606930</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
@@ -44694,7 +44694,7 @@
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666822</t>
+          <t xml:space="preserve">311666811</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
@@ -44934,7 +44934,7 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666762</t>
+          <t xml:space="preserve">311666811</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
@@ -45234,7 +45234,7 @@
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667588</t>
+          <t xml:space="preserve">311667587</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
@@ -56814,7 +56814,7 @@
       </c>
       <c r="I947" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750229</t>
+          <t xml:space="preserve">311750228</t>
         </is>
       </c>
       <c r="J947" t="inlineStr">
@@ -56934,7 +56934,7 @@
       </c>
       <c r="I949" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750172</t>
+          <t xml:space="preserve">311750173</t>
         </is>
       </c>
       <c r="J949" t="inlineStr">
@@ -58194,7 +58194,7 @@
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751651</t>
+          <t xml:space="preserve">311751653</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">

--- a/public/exports/64942212.xlsx
+++ b/public/exports/64942212.xlsx
@@ -12469,7 +12469,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031569</t>
+          <t xml:space="preserve">311031555</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031569</t>
+          <t xml:space="preserve">311031555</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311031569</t>
+          <t xml:space="preserve">311031555</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087931</t>
+          <t xml:space="preserve">311087929</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087931</t>
+          <t xml:space="preserve">311087930</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -40094,12 +40094,12 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606929</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K617" t="inlineStr">
@@ -40159,12 +40159,12 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606929</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K618" t="inlineStr">
@@ -40289,12 +40289,12 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606931</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K620" t="inlineStr">
@@ -40354,12 +40354,12 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606925</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
@@ -40614,12 +40614,12 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606932</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K625" t="inlineStr">
@@ -40679,12 +40679,12 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606932</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K626" t="inlineStr">
@@ -40744,12 +40744,12 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606930</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -42564,7 +42564,7 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607314</t>
+          <t xml:space="preserve">311607313</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
@@ -42694,7 +42694,7 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607314</t>
+          <t xml:space="preserve">311607313</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642581</t>
+          <t xml:space="preserve">311642575</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -46009,7 +46009,7 @@
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642577</t>
+          <t xml:space="preserve">311642575</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
@@ -46074,7 +46074,7 @@
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642581</t>
+          <t xml:space="preserve">311642575</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
@@ -48414,7 +48414,7 @@
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666822</t>
+          <t xml:space="preserve">311666811</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
@@ -49519,7 +49519,7 @@
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671591</t>
+          <t xml:space="preserve">311671586</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
@@ -51404,7 +51404,7 @@
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t xml:space="preserve">311681942</t>
+          <t xml:space="preserve">311681941</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
@@ -53419,7 +53419,7 @@
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722451</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
@@ -53484,7 +53484,7 @@
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722451</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
@@ -53614,7 +53614,7 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722474</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
@@ -61674,7 +61674,7 @@
       </c>
       <c r="I949" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750173</t>
+          <t xml:space="preserve">311750172</t>
         </is>
       </c>
       <c r="J949" t="inlineStr">
@@ -63039,7 +63039,7 @@
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751653</t>
+          <t xml:space="preserve">311751651</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
@@ -65574,12 +65574,12 @@
       </c>
       <c r="I1009" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761230</t>
+          <t xml:space="preserve">311761210</t>
         </is>
       </c>
       <c r="J1009" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="K1009" t="inlineStr">
@@ -66549,7 +66549,7 @@
       </c>
       <c r="I1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771387</t>
+          <t xml:space="preserve">311771382</t>
         </is>
       </c>
       <c r="J1024" t="inlineStr">
@@ -66614,7 +66614,7 @@
       </c>
       <c r="I1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771387</t>
+          <t xml:space="preserve">311771383</t>
         </is>
       </c>
       <c r="J1025" t="inlineStr">
